--- a/outputs/tables/TableS18_SynGO_BP_partitions.xlsx
+++ b/outputs/tables/TableS18_SynGO_BP_partitions.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
-    <t>Table S14. Mutation rates and contrasts of these rates for independent subsets of genes formed from major children of process of the synapse. In the upper triangle, the ratio of de novo rates in ASD cases (column gene set divided row gene set). In the lower triangle, p-values assuming a binomial distribution for mutations. Rightmost table, number of genes per set; number of de novo mutations identified in ASD cases; and the ratio of these to form a rate. Pre=process in the presynapse; Post= process in the postsynapse; Sig= synaptic signaling; Org= synapse organization; Oth= Metabolism &amp; Transport.</t>
+    <t>Mutation rates and contrasts of these rates for independent subsets of genes formed from major children of process of the synapse. In the upper triangle, the ratio of de novo rates in ASD cases (column gene set divided row gene set). In the lower triangle, p-values assuming a binomial distribution for mutations. Rightmost table, number of genes per set; number of de novo mutations identified in ASD cases; and the ratio of these to form a rate. Pre=process in the presynapse; Post= process in the postsynapse; Sig= synaptic signaling; Org= synapse organization; Oth= Metabolism &amp; Transport.</t>
   </si>
   <si>
     <t>Pre</t>
